--- a/dati_20_loci.xlsx
+++ b/dati_20_loci.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -56,19 +56,33 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="13"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -201,31 +215,234 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$Z$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10626</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>42504</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>134596</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>346104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>735471</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1307504</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1961256</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2496144</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2704156</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2496144</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1961256</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1307504</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>735471</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>346104</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>134596</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>42504</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10626</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>276</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="48228323"/>
+        <c:axId val="63889171"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48228323"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="63889171"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="63889171"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
                 <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Distribuzione di probabilità cumulativa</a:t>
-            </a:r>
+              </a:defRPr>
+            </a:pPr>
           </a:p>
-        </c:rich>
-      </c:tx>
+        </c:txPr>
+        <c:crossAx val="48228323"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -233,8 +450,299 @@
           <a:noFill/>
         </a:ln>
       </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$3:$Z$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>5.96046447753906E-008</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.43051147460938E-006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.64508819580078E-005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.000120639801025391</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.000633358955383301</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0025334358215332</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.00802254676818848</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.0206294059753418</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.0438374876976013</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.0779333114624023</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.116899967193604</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.148781776428223</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.161180257797241</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.148781776428223</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.116899967193604</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.0779333114624023</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.0438374876976013</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.0206294059753418</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.00802254676818848</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.0025334358215332</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.000633358955383301</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.000120639801025391</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.64508819580078E-005</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.43051147460938E-006</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.96046447753906E-008</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="100"/>
+        <c:overlap val="0"/>
+        <c:axId val="96534855"/>
+        <c:axId val="5861312"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="96534855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="5861312"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="5861312"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="96534855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:barChart>
         <c:barDir val="col"/>
@@ -365,44 +873,16 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="0"/>
-        <c:axId val="4909026"/>
-        <c:axId val="94667128"/>
+        <c:axId val="79211639"/>
+        <c:axId val="45637875"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4909026"/>
+        <c:axId val="79211639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Valori fenotipici</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -425,7 +905,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94667128"/>
+        <c:crossAx val="45637875"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -433,7 +913,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94667128"/>
+        <c:axId val="45637875"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -448,34 +928,6 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Probabilità cumulativa</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -498,7 +950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4909026"/>
+        <c:crossAx val="79211639"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -546,45 +998,15 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Distribuzione di frequenza relativa</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:areaChart>
+        <c:grouping val="standard"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -596,7 +1018,6 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:txPr>
               <a:bodyPr wrap="none"/>
@@ -609,7 +1030,6 @@
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -625,129 +1045,96 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$3:$Z$3</c:f>
+              <c:f>Sheet1!$B$4:$Y$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>5.96046447753906E-008</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.43051147460938E-006</c:v>
+                  <c:v>1.49011611938477E-006</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.64508819580078E-005</c:v>
+                  <c:v>1.79409980773926E-005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.000120639801025391</c:v>
+                  <c:v>0.000138580799102783</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.000633358955383301</c:v>
+                  <c:v>0.000771939754486084</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0025334358215332</c:v>
+                  <c:v>0.00330537557601929</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.00802254676818848</c:v>
+                  <c:v>0.0113279223442078</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0206294059753418</c:v>
+                  <c:v>0.0319573283195496</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0438374876976013</c:v>
+                  <c:v>0.0757948160171509</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.0779333114624023</c:v>
+                  <c:v>0.153728127479553</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.116899967193604</c:v>
+                  <c:v>0.270628094673157</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.148781776428223</c:v>
+                  <c:v>0.419409871101379</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.161180257797241</c:v>
+                  <c:v>0.580590128898621</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.148781776428223</c:v>
+                  <c:v>0.729371905326843</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.116899967193604</c:v>
+                  <c:v>0.846271872520447</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.0779333114624023</c:v>
+                  <c:v>0.924205183982849</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.0438374876976013</c:v>
+                  <c:v>0.96804267168045</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.0206294059753418</c:v>
+                  <c:v>0.988672077655792</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.00802254676818848</c:v>
+                  <c:v>0.996694624423981</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0025334358215332</c:v>
+                  <c:v>0.999228060245514</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.000633358955383301</c:v>
+                  <c:v>0.999861419200897</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.000120639801025391</c:v>
+                  <c:v>0.999982059001923</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.64508819580078E-005</c:v>
+                  <c:v>0.999998509883881</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.43051147460938E-006</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>5.96046447753906E-008</c:v>
+                  <c:v>0.999999940395355</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:gapWidth val="100"/>
-        <c:overlap val="0"/>
-        <c:axId val="58954930"/>
-        <c:axId val="59867559"/>
-      </c:barChart>
+        <c:axId val="40336529"/>
+        <c:axId val="73536255"/>
+      </c:areaChart>
       <c:catAx>
-        <c:axId val="58954930"/>
+        <c:axId val="40336529"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Valori fenotipici</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -770,7 +1157,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59867559"/>
+        <c:crossAx val="73536255"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -778,7 +1165,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59867559"/>
+        <c:axId val="73536255"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -793,34 +1180,6 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Frequenza relativa</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -843,9 +1202,9 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58954930"/>
+        <c:crossAx val="40336529"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -878,7 +1237,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
+    <c:dispBlanksAs val="zero"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -891,40 +1250,12 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Distribuzione di frequenza relativa</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:areaChart>
         <c:grouping val="standard"/>
@@ -1049,44 +1380,16 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="92163313"/>
-        <c:axId val="13151050"/>
+        <c:axId val="62112847"/>
+        <c:axId val="7593223"/>
       </c:areaChart>
       <c:catAx>
-        <c:axId val="92163313"/>
+        <c:axId val="62112847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Valori fenotipici</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -1109,7 +1412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13151050"/>
+        <c:crossAx val="7593223"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1117,7 +1420,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="13151050"/>
+        <c:axId val="7593223"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1132,34 +1435,6 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Frequenza relativa</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -1182,346 +1457,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92163313"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
-          </a:solidFill>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Distribuzione di probabilità cumulativa</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:areaChart>
-        <c:grouping val="standard"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$4:$Z$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
-                <c:pt idx="0">
-                  <c:v>5.96046447753906E-008</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.49011611938477E-006</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.79409980773926E-005</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.000138580799102783</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.000771939754486084</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.00330537557601929</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.0113279223442078</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.0319573283195496</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.0757948160171509</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.153728127479553</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.270628094673157</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.419409871101379</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.580590128898621</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.729371905326843</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.846271872520447</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.924205183982849</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.96804267168045</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.988672077655792</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.996694624423981</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.999228060245514</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.999861419200897</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.999982059001923</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.999998509883881</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.999999940395355</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:axId val="80406502"/>
-        <c:axId val="44192043"/>
-      </c:areaChart>
-      <c:catAx>
-        <c:axId val="80406502"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Valori fenotipici</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="44192043"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="44192043"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Frequenza relativa</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="80406502"/>
+        <c:crossAx val="62112847"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1573,16 +1509,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>13680</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>20520</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>5760</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>12240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>527400</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>20880</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>519480</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1590,7 +1526,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7506720" y="782640"/>
+        <a:off x="14242320" y="964800"/>
         <a:ext cx="5758920" cy="3238920"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1603,16 +1539,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>12960</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>76680</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>296640</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>128520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>526680</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>77040</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>61200</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>128880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1620,7 +1556,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7506000" y="3886560"/>
+        <a:off x="10037520" y="11748960"/>
         <a:ext cx="5758920" cy="3238920"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1633,16 +1569,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>669960</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>180000</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>448920</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>171360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>434880</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>180720</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>213480</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>171720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1650,8 +1586,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="669960" y="3989880"/>
-        <a:ext cx="5759280" cy="3239280"/>
+        <a:off x="7192800" y="4933800"/>
+        <a:ext cx="5758920" cy="3238920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1663,16 +1599,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>671040</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>91800</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>640440</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>5040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>435960</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>92520</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>405000</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>5400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1680,8 +1616,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="671040" y="853920"/>
-        <a:ext cx="5759280" cy="3239280"/>
+        <a:off x="4386960" y="8386920"/>
+        <a:ext cx="5758920" cy="3238920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1689,6 +1625,793 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>647640</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>100080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>412560</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>100800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4394160" y="11720520"/>
+        <a:ext cx="5759280" cy="3239280"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>343800</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>103680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>344160</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>190440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7087680" y="9628560"/>
+          <a:ext cx="360" cy="2563560"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>428400</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>71640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>282960</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>55800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6422760" y="8834760"/>
+          <a:ext cx="1353240" cy="2460600"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="36720">
+          <a:solidFill>
+            <a:srgbClr val="ff8000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>244800</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>15840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>703440</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>23760</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3991320" y="10112400"/>
+          <a:ext cx="3456000" cy="7920"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>715320</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>16200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>716040</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>15840</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6709680" y="12779640"/>
+          <a:ext cx="720" cy="1904760"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>537120</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>61200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>514800</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>26280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5782320" y="13396320"/>
+          <a:ext cx="726840" cy="345960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="90000" rIns="90000" tIns="45000" bIns="45000" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Noto Sans CJK SC"/>
+            </a:rPr>
+            <a:t>dy/dx</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>275400</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>150480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>577440</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>180000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7019280" y="10437480"/>
+          <a:ext cx="1800360" cy="601200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="90000" rIns="90000" tIns="45000" bIns="45000" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="ffffff"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Noto Sans CJK SC"/>
+            </a:rPr>
+            <a:t>dy = probabilità </a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="ffffff"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Noto Sans CJK SC"/>
+            </a:rPr>
+            <a:t>cumulativa</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>374760</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>15480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>351720</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>45360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5619960" y="9731160"/>
+          <a:ext cx="726120" cy="601200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="90000" rIns="90000" tIns="45000" bIns="45000" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="ff0000"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Noto Sans CJK SC"/>
+            </a:rPr>
+            <a:t>dx</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:endParaRPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>525240</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>169200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>22680</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>174600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6519600" y="14647320"/>
+          <a:ext cx="246960" cy="5400"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>420840</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>70560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>93240</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>35640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6415200" y="14929560"/>
+          <a:ext cx="421920" cy="345960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="000000"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr lIns="90000" rIns="90000" tIns="45000" bIns="45000" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="ffffff"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Noto Sans CJK SC"/>
+            </a:rPr>
+            <a:t>dx</a:t>
+          </a:r>
+          <a:endParaRPr b="0" lang="en-US" sz="1800" spc="-1" strike="noStrike">
+            <a:latin typeface="Times New Roman"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>525600</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>35280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>532440</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>162000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6519960" y="12798720"/>
+          <a:ext cx="6840" cy="1841400"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>518400</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>28800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>15840</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>34200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6512760" y="12792240"/>
+          <a:ext cx="246960" cy="5400"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>155160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>350280</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7065720" y="12156840"/>
+          <a:ext cx="28440" cy="2497320"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>504360</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>155160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>532800</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>176040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7248240" y="12156840"/>
+          <a:ext cx="28440" cy="2497320"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>294120</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>155880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>541080</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>161280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7038000" y="12157560"/>
+          <a:ext cx="246960" cy="5400"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>307800</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>163080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>554760</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>168480</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name=""/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7051680" y="14641200"/>
+          <a:ext cx="246960" cy="5400"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="18360">
+          <a:solidFill>
+            <a:srgbClr val="ff0000"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
